--- a/images/kica1.xlsx
+++ b/images/kica1.xlsx
@@ -103,32 +103,32 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>작품제목( ※ 필수 )</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>기관정보 ( ※ 필수 )</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>『 대한민국 국제 어린이 미술 대회 』 단체 참가작 명단</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
+    <t>기관정보</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>제목(※필수/공백포함 25자 이내)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve"> * 참가작 명단 ( 작품 뒷면에 ‘</t>
+      <t xml:space="preserve"> * </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FFFF00FF"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>기관명(학원명), 기관연락처, 학생명, 학년(유치부는 연령)</t>
+      <t>작품 뒷면 기재사항</t>
     </r>
     <r>
       <rPr>
@@ -139,13 +139,57 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>’ 동일하게 기재, 동명이인일 경우 ‘</t>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>기관명(학원명), 기관연락처, 학생명, 학년(해외·비진학 어린이는 연령 기재)</t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="9"/>
-        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>동명이인일 경우</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
@@ -162,20 +206,17 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">’ 추가 기재 )
-   - </t>
+      <t xml:space="preserve"> </t>
     </r>
     <r>
       <rPr>
-        <b/>
         <sz val="9"/>
-        <color rgb="FFFF0000"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>상장 기재 소속</t>
+      <t>추가 기재 )</t>
     </r>
     <r>
       <rPr>
@@ -186,30 +227,18 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">: ‘교습소’ 표기를 원하지 않으시면 제외하여 작성. 학교명으로 기재되길 원하시면 학교명을 작성. </t>
+      <t xml:space="preserve">
+ </t>
     </r>
     <r>
       <rPr>
-        <b/>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>상장, 액자, 상패 모두 기재한 소속명</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
         <sz val="9"/>
         <rFont val="맑은 고딕"/>
         <family val="3"/>
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>이 인쇄됩니다.</t>
+      <t xml:space="preserve">  - 상장 기재 소속: ‘교습소’ 표기를 원하지 않으시면 제외하여 작성. 학교명으로 기재되길 원하시면 학교명을 작성. 상장, 액자, 상패 모두 기재한 소속명이 인쇄됩니다.</t>
     </r>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -218,7 +247,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,7 +301,6 @@
     <font>
       <b/>
       <sz val="9"/>
-      <color rgb="FFFF0000"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -280,6 +308,23 @@
     </font>
     <font>
       <b/>
+      <sz val="9"/>
+      <color rgb="FFFF00FF"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="9"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -422,14 +467,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -437,6 +482,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF00FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -726,13 +776,13 @@
     <col min="10" max="10" width="13.5625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="6.125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.6875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="30.375" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="31.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="43.15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="7" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -743,38 +793,40 @@
       <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:14" ht="33" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
     </row>
     <row r="3" spans="1:14" ht="19.149999999999999" x14ac:dyDescent="0.6">
       <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="10"/>
-      <c r="D3" s="10"/>
-      <c r="E3" s="10"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="9" t="s">
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
+      <c r="H3" s="9"/>
+      <c r="I3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
     </row>
     <row r="4" spans="1:14" ht="30.85" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="6"/>
@@ -812,7 +864,7 @@
         <v>4</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N4" s="4" t="s">
         <v>5</v>
@@ -1742,9 +1794,9 @@
   <mergeCells count="5">
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:H2"/>
     <mergeCell ref="I3:N3"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="A2:J2"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
